--- a/Region_data.xlsx
+++ b/Region_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\GITHUBS\contact_wire_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\githubs\contact_wire_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB04D36-D94D-402F-92F1-B1C3B6830584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC2A815-3027-4EC6-A686-E70F05221A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="10" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="carlisle_notes" sheetId="8" r:id="rId6"/>
     <sheet name="test_NS" sheetId="13" r:id="rId7"/>
     <sheet name="test_operators" sheetId="11" r:id="rId8"/>
+    <sheet name="Scotland_NS_Notes" sheetId="15" r:id="rId9"/>
+    <sheet name="Scotland_operators" sheetId="16" r:id="rId10"/>
+    <sheet name="Scotland_NS" sheetId="17" r:id="rId11"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="372">
   <si>
     <t>neutral section names</t>
   </si>
@@ -305,13 +308,856 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>GF/10/28</t>
+  </si>
+  <si>
+    <t>RSL1</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>GG/00/07</t>
+  </si>
+  <si>
+    <t>RCB</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>GG/00/08</t>
+  </si>
+  <si>
+    <t>FX/00/16</t>
+  </si>
+  <si>
+    <t>GHE</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>GL/4/04</t>
+  </si>
+  <si>
+    <t>WWD</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>GL/3/04</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>GL5/03</t>
+  </si>
+  <si>
+    <t>EGS2</t>
+  </si>
+  <si>
+    <t>GL6/5F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>G/619/33</t>
+  </si>
+  <si>
+    <t>WCM2</t>
+  </si>
+  <si>
+    <t>G/619/34</t>
+  </si>
+  <si>
+    <t>GK</t>
+  </si>
+  <si>
+    <t>GK04/50A</t>
+  </si>
+  <si>
+    <t>KHL</t>
+  </si>
+  <si>
+    <t>GK04/04A</t>
+  </si>
+  <si>
+    <t>HMN2</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>GEN/00/16</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>G/513/3</t>
+  </si>
+  <si>
+    <t>G/636/17</t>
+  </si>
+  <si>
+    <t>G/599/42A</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>G/566/03</t>
+  </si>
+  <si>
+    <t>G599/17A</t>
+  </si>
+  <si>
+    <t>GES/00/08</t>
+  </si>
+  <si>
+    <t>ECA1</t>
+  </si>
+  <si>
+    <t>GES/00/09</t>
+  </si>
+  <si>
+    <t>G/566/04</t>
+  </si>
+  <si>
+    <t>G/540/25</t>
+  </si>
+  <si>
+    <t>G/540/26</t>
+  </si>
+  <si>
+    <t>GD/12/04</t>
+  </si>
+  <si>
+    <t>SCM3</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>EG/28/19</t>
+  </si>
+  <si>
+    <t>EGM1</t>
+  </si>
+  <si>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>GD/28/09</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>FS/00/02B</t>
+  </si>
+  <si>
+    <t>SGN</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>FT/00/04</t>
+  </si>
+  <si>
+    <t>CBD2</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+  <si>
+    <t>FT/11/28</t>
+  </si>
+  <si>
+    <t>CBD1</t>
+  </si>
+  <si>
+    <t>ES/01/20</t>
+  </si>
+  <si>
+    <t>SAA</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>GD/32/34</t>
+  </si>
+  <si>
+    <t>GD/48/13</t>
+  </si>
+  <si>
+    <t>PMT</t>
+  </si>
+  <si>
+    <t>F/12/31</t>
+  </si>
+  <si>
+    <t>NEM2</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>B/02/05</t>
+  </si>
+  <si>
+    <t>ARG2</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>NEM3</t>
+  </si>
+  <si>
+    <t>F/01/41</t>
+  </si>
+  <si>
+    <t>RN3G</t>
+  </si>
+  <si>
+    <t>RN4A</t>
+  </si>
+  <si>
+    <t>GDC/00/03A</t>
+  </si>
+  <si>
+    <t>CMS</t>
+  </si>
+  <si>
+    <t>GDC</t>
+  </si>
+  <si>
+    <t>EP/00/20</t>
+  </si>
+  <si>
+    <t>EP</t>
+  </si>
+  <si>
+    <t>EP/00/21</t>
+  </si>
+  <si>
+    <t>GL7/04</t>
+  </si>
+  <si>
+    <t>GL7/05</t>
+  </si>
+  <si>
+    <t>GE/42/10A</t>
+  </si>
+  <si>
+    <t>ECA3</t>
+  </si>
+  <si>
+    <t>BH3</t>
+  </si>
+  <si>
+    <t>NBE</t>
+  </si>
+  <si>
+    <t>CH6G/BH4</t>
+  </si>
+  <si>
+    <t>E626/22A</t>
+  </si>
+  <si>
+    <t>ECM8</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F/31/32</t>
+  </si>
+  <si>
+    <t>NEM1</t>
+  </si>
+  <si>
+    <t>PC2K</t>
+  </si>
+  <si>
+    <t>EGM2</t>
+  </si>
+  <si>
+    <t>CH5B</t>
+  </si>
+  <si>
+    <t>RW/0/16</t>
+  </si>
+  <si>
+    <t>RNC</t>
+  </si>
+  <si>
+    <t>RW</t>
+  </si>
+  <si>
+    <t>LA/02/14</t>
+  </si>
+  <si>
+    <t>AYR3</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>K00/20</t>
+  </si>
+  <si>
+    <t>CTC</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>K/00/20</t>
+  </si>
+  <si>
+    <t>MEN2</t>
+  </si>
+  <si>
+    <t>EK</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L00/100A</t>
+  </si>
+  <si>
+    <t>AYR1</t>
+  </si>
+  <si>
+    <t>HST</t>
+  </si>
+  <si>
+    <t>LANGLOAN JUNCTION</t>
+  </si>
+  <si>
+    <t>HOLYTOWN JN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOWKTHRAPPLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIRKHILL </t>
+  </si>
+  <si>
+    <t>CARSTAIRS</t>
+  </si>
+  <si>
+    <t>ECCLEFECHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEWTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELVANFOOT </t>
+  </si>
+  <si>
+    <t>ELVANFOOT</t>
+  </si>
+  <si>
+    <t>MURTHAT</t>
+  </si>
+  <si>
+    <t>GREENHILL FS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELLGROVE JUNCTION </t>
+  </si>
+  <si>
+    <t>SIGHTHILL</t>
+  </si>
+  <si>
+    <t>KINCARDINE</t>
+  </si>
+  <si>
+    <t>PERTH</t>
+  </si>
+  <si>
+    <t>STIRLING BRIDGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRUMGELLOCH </t>
+  </si>
+  <si>
+    <t>PARKHEAD</t>
+  </si>
+  <si>
+    <t>MIDCALDER JUNCTION</t>
+  </si>
+  <si>
+    <t>NEWBRIDGE</t>
+  </si>
+  <si>
+    <t>MUSSELBURGH</t>
+  </si>
+  <si>
+    <t>BATHGATE FS</t>
+  </si>
+  <si>
+    <t>HAYMARKET</t>
+  </si>
+  <si>
+    <t>FERGUSLIE FS</t>
+  </si>
+  <si>
+    <t>SHIELDS JUNCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINNIESTON </t>
+  </si>
+  <si>
+    <t>MUIRHOUSE JN</t>
+  </si>
+  <si>
+    <t>GRHMSTON</t>
+  </si>
+  <si>
+    <t>DOWN Main</t>
+  </si>
+  <si>
+    <t>Up Main G(WCM1)</t>
+  </si>
+  <si>
+    <t>DOWN Main G(WCM1)</t>
+  </si>
+  <si>
+    <t>Up Main GE(ECA1)</t>
+  </si>
+  <si>
+    <t>DOWN Main GE(ECA1)</t>
+  </si>
+  <si>
+    <t>Reversible Slow(CSP)</t>
+  </si>
+  <si>
+    <t>Reversible Fast(CSP)</t>
+  </si>
+  <si>
+    <t>Up Main(SCM3)</t>
+  </si>
+  <si>
+    <t>Up Main(GHL)</t>
+  </si>
+  <si>
+    <t>DOWN Main(SCM3)</t>
+  </si>
+  <si>
+    <t>DOWN Main(GHL)</t>
+  </si>
+  <si>
+    <t>Up Main(NEM3)</t>
+  </si>
+  <si>
+    <t>DOWN Main(NEM3)</t>
+  </si>
+  <si>
+    <t>Up Main(BAK)</t>
+  </si>
+  <si>
+    <t>DOWN Main(BAK)</t>
+  </si>
+  <si>
+    <t>Up Main(CTC)</t>
+  </si>
+  <si>
+    <t>DOWN Main(CTC)</t>
+  </si>
+  <si>
+    <t>ARGYLE DOWN Main</t>
+  </si>
+  <si>
+    <t>UP Main (RSL1)</t>
+  </si>
+  <si>
+    <t>DOWN Main (RSL1)</t>
+  </si>
+  <si>
+    <t>UP Main (RCB1)</t>
+  </si>
+  <si>
+    <t>DOWN Main (RCB1)</t>
+  </si>
+  <si>
+    <t>Up Main (WWD)</t>
+  </si>
+  <si>
+    <t>DOWN Main (WWD)</t>
+  </si>
+  <si>
+    <t>Up Main (EGS)</t>
+  </si>
+  <si>
+    <t>DOWN Main (EGS)</t>
+  </si>
+  <si>
+    <t>GREENHILL LWR Junction</t>
+  </si>
+  <si>
+    <t>GARNQUEEN</t>
+  </si>
+  <si>
+    <t>Up Main(NORTH)</t>
+  </si>
+  <si>
+    <t>DOWN Main(NORTH)</t>
+  </si>
+  <si>
+    <t>Up Main(Junction)</t>
+  </si>
+  <si>
+    <t>DOWN Main(Junction)</t>
+  </si>
+  <si>
+    <t>Up Main(NBE)</t>
+  </si>
+  <si>
+    <t>DOWN Main(NBE)</t>
+  </si>
+  <si>
+    <t>NEWTON</t>
+  </si>
+  <si>
+    <t>DOWN Slow (WEST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSS-EAST </t>
+  </si>
+  <si>
+    <t>CARMUIRS JUNCTION</t>
+  </si>
+  <si>
+    <t>POLMONT JUNCTION</t>
+  </si>
+  <si>
+    <t>SLATEFORD</t>
+  </si>
+  <si>
+    <t>GARTCOSH</t>
+  </si>
+  <si>
+    <t>Bi dir single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUTHERGLEN </t>
+  </si>
+  <si>
+    <t>Curve (Bi dir single)</t>
+  </si>
+  <si>
+    <t>Up Main(AYR)</t>
+  </si>
+  <si>
+    <t>DOWN Main(AYR)</t>
+  </si>
+  <si>
+    <t>Up Main(City Union)</t>
+  </si>
+  <si>
+    <t>DOWN Main(City Union)</t>
+  </si>
+  <si>
+    <t>Alan Anderson</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>Alasdair Lannigan</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>Gillian Crisp</t>
+  </si>
+  <si>
+    <t>gc</t>
+  </si>
+  <si>
+    <t>Sean O'Neill</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>Ryan Leggat</t>
+  </si>
+  <si>
+    <t>rl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kenny </t>
+  </si>
+  <si>
+    <t>wk</t>
+  </si>
+  <si>
+    <t>John Goodyear</t>
+  </si>
+  <si>
+    <t>jg</t>
+  </si>
+  <si>
+    <t>Henry Ewart</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steven Dunn </t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graeme Beattie </t>
+  </si>
+  <si>
+    <t>gb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gary Henderson </t>
+  </si>
+  <si>
+    <t>gh</t>
+  </si>
+  <si>
+    <t>Bathgate Fs</t>
+  </si>
+  <si>
+    <t>Bellgrove Junction</t>
+  </si>
+  <si>
+    <t>Carmuirs Junction</t>
+  </si>
+  <si>
+    <t>Carstairs</t>
+  </si>
+  <si>
+    <t>Reversible Slow(Csp)</t>
+  </si>
+  <si>
+    <t>Reversible Fast(Csp)</t>
+  </si>
+  <si>
+    <t>Up Main G(Wcm1)</t>
+  </si>
+  <si>
+    <t>Down Main G(Wcm1)</t>
+  </si>
+  <si>
+    <t>Up Main Ge(Eca1)</t>
+  </si>
+  <si>
+    <t>Down Main Ge(Eca1)</t>
+  </si>
+  <si>
+    <t>Drumgelloch</t>
+  </si>
+  <si>
+    <t>Ecclefechan</t>
+  </si>
+  <si>
+    <t>Elvanfoot</t>
+  </si>
+  <si>
+    <t>Ferguslie Fs</t>
+  </si>
+  <si>
+    <t>Finnieston</t>
+  </si>
+  <si>
+    <t>Argyle Down Main</t>
+  </si>
+  <si>
+    <t>Up Main(Nem3)</t>
+  </si>
+  <si>
+    <t>Down Main(Nem3)</t>
+  </si>
+  <si>
+    <t>Garnqueen</t>
+  </si>
+  <si>
+    <t>Up Main(North)</t>
+  </si>
+  <si>
+    <t>Down Main(North)</t>
+  </si>
+  <si>
+    <t>Down Main(Junction)</t>
+  </si>
+  <si>
+    <t>Gartcosh</t>
+  </si>
+  <si>
+    <t>Bi Dir Single</t>
+  </si>
+  <si>
+    <t>Gowkthrapple</t>
+  </si>
+  <si>
+    <t>Greenhill Fs</t>
+  </si>
+  <si>
+    <t>Greenhill Lwr Junction</t>
+  </si>
+  <si>
+    <t>Up Main(Scm3)</t>
+  </si>
+  <si>
+    <t>Down Main(Scm3)</t>
+  </si>
+  <si>
+    <t>Up Main(Ghl)</t>
+  </si>
+  <si>
+    <t>Down Main(Ghl)</t>
+  </si>
+  <si>
+    <t>Grhmston</t>
+  </si>
+  <si>
+    <t>Haymarket</t>
+  </si>
+  <si>
+    <t>Holytown Jn</t>
+  </si>
+  <si>
+    <t>Up Main (Wwd)</t>
+  </si>
+  <si>
+    <t>Down Main (Wwd)</t>
+  </si>
+  <si>
+    <t>Up Main (Egs)</t>
+  </si>
+  <si>
+    <t>Down Main (Egs)</t>
+  </si>
+  <si>
+    <t>Kincardine</t>
+  </si>
+  <si>
+    <t>Kirkhill</t>
+  </si>
+  <si>
+    <t>Langloan Junction</t>
+  </si>
+  <si>
+    <t>Up Main (Rsl1)</t>
+  </si>
+  <si>
+    <t>Down Main (Rsl1)</t>
+  </si>
+  <si>
+    <t>Up Main (Rcb1)</t>
+  </si>
+  <si>
+    <t>Down Main (Rcb1)</t>
+  </si>
+  <si>
+    <t>Midcalder Junction</t>
+  </si>
+  <si>
+    <t>Muirhouse Jn</t>
+  </si>
+  <si>
+    <t>Up Main(Bak)</t>
+  </si>
+  <si>
+    <t>Down Main(Bak)</t>
+  </si>
+  <si>
+    <t>Up Main(Ctc)</t>
+  </si>
+  <si>
+    <t>Down Main(Ctc)</t>
+  </si>
+  <si>
+    <t>Murthat</t>
+  </si>
+  <si>
+    <t>Musselburgh</t>
+  </si>
+  <si>
+    <t>Newbridge</t>
+  </si>
+  <si>
+    <t>Up Main(Nbe)</t>
+  </si>
+  <si>
+    <t>Down Main(Nbe)</t>
+  </si>
+  <si>
+    <t>Newton</t>
+  </si>
+  <si>
+    <t>Down Slow (West)</t>
+  </si>
+  <si>
+    <t>Ross-East</t>
+  </si>
+  <si>
+    <t>Parkhead</t>
+  </si>
+  <si>
+    <t>Perth</t>
+  </si>
+  <si>
+    <t>Polmont Junction</t>
+  </si>
+  <si>
+    <t>Rutherglen</t>
+  </si>
+  <si>
+    <t>Curve (Bi Dir Single)</t>
+  </si>
+  <si>
+    <t>Shields Junction</t>
+  </si>
+  <si>
+    <t>Up Main(Ayr)</t>
+  </si>
+  <si>
+    <t>Down Main(Ayr)</t>
+  </si>
+  <si>
+    <t>Down Main(City Union)</t>
+  </si>
+  <si>
+    <t>Sighthill</t>
+  </si>
+  <si>
+    <t>Slateford</t>
+  </si>
+  <si>
+    <t>Stirling Bridge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,6 +1186,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -364,10 +1232,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -392,9 +1262,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{A31FC1C9-2C22-4D43-BBBE-766A829A4011}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{CF500470-38AD-498A-8470-1AFFD93F0C30}"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
@@ -1146,6 +2049,2493 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB9595C-2F56-4A35-B58C-E2852054D35F}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2">
+        <v>1161419</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3">
+        <v>1317648</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4">
+        <v>1349812</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5">
+        <v>1372275</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6">
+        <v>1218733</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7">
+        <v>574535</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8">
+        <v>120340</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="B9">
+        <v>120212</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10">
+        <v>622047</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11">
+        <v>574509</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="B12">
+        <v>590336</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC72428-B456-4DFD-ADB1-141C1F46B28E}">
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" style="20" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="20" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="20" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D2" s="20">
+        <v>107</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="20">
+        <v>6737415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D3" s="20">
+        <v>107</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="20">
+        <v>6737416</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D4" s="20">
+        <v>107</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="20">
+        <v>18771404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D5" s="20">
+        <v>107</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="20">
+        <v>18771405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D6" s="20">
+        <v>107</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="20">
+        <v>18839472</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D7" s="20">
+        <v>107</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="20">
+        <v>18839473</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C8" s="20">
+        <v>3200</v>
+      </c>
+      <c r="D8" s="20">
+        <v>107</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="20">
+        <v>677079</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C9" s="20">
+        <v>3100</v>
+      </c>
+      <c r="D9" s="20">
+        <v>107</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="20">
+        <v>677113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D10" s="20">
+        <v>107</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="20">
+        <v>677168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D11" s="20">
+        <v>107</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="20">
+        <v>677140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D12" s="20">
+        <v>107</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="20">
+        <v>677149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D13" s="20">
+        <v>107</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="20">
+        <v>677148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D14" s="20">
+        <v>107</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="20">
+        <v>6737419</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D15" s="20">
+        <v>107</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="20">
+        <v>6737420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D16" s="20">
+        <v>107</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="20">
+        <v>677105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="20">
+        <v>107</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="20">
+        <v>677114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D18" s="20">
+        <v>107</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="20">
+        <v>677153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D19" s="20">
+        <v>107</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="20">
+        <v>677124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D20" s="20">
+        <v>107</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H20" s="20">
+        <v>19470810</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D21" s="20">
+        <v>107</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H21" s="20">
+        <v>19470811</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="C22" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D22" s="20">
+        <v>107</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="20">
+        <v>677138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D23" s="20">
+        <v>107</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="20">
+        <v>677141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C24" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D24" s="20">
+        <v>107</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="20">
+        <v>677150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="C25" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D25" s="20">
+        <v>107</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" s="20">
+        <v>9697138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C26" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D26" s="20">
+        <v>107</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" s="20">
+        <v>9697137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D27" s="20">
+        <v>107</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" s="20">
+        <v>18772023</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D28" s="20">
+        <v>107</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" s="20">
+        <v>18772024</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="20">
+        <v>3400</v>
+      </c>
+      <c r="D29" s="20">
+        <v>107</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="20">
+        <v>18772025</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D30" s="20">
+        <v>107</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="20">
+        <v>19289126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D31" s="20">
+        <v>107</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="20">
+        <v>19289125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D32" s="20">
+        <v>107</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="20">
+        <v>18748267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D33" s="20">
+        <v>107</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H33" s="20">
+        <v>18748268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="C34" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D34" s="20">
+        <v>107</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" s="20">
+        <v>18748269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="C35" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D35" s="20">
+        <v>107</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35" s="20">
+        <v>18748270</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="C36" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D36" s="20">
+        <v>107</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="20">
+        <v>18748271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="C37" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D37" s="20">
+        <v>107</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="20">
+        <v>18748272</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D38" s="20">
+        <v>107</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="20">
+        <v>18905788</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D39" s="20">
+        <v>107</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="20">
+        <v>18905787</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D40" s="20">
+        <v>107</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H40" s="20">
+        <v>6737417</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D41" s="20">
+        <v>107</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H41" s="20">
+        <v>6737418</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="C42" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D42" s="20">
+        <v>107</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" s="20">
+        <v>19044113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="C43" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D43" s="20">
+        <v>107</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H43" s="20">
+        <v>19044114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D44" s="20">
+        <v>107</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H44" s="20">
+        <v>19044115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="C45" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D45" s="20">
+        <v>107</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H45" s="20">
+        <v>19044116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D46" s="20">
+        <v>107</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="20">
+        <v>18905782</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D47" s="20">
+        <v>107</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="20">
+        <v>18905781</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D48" s="20">
+        <v>107</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H48" s="20">
+        <v>19865894</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D49" s="20">
+        <v>107</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H49" s="20">
+        <v>19865893</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="C50" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D50" s="20">
+        <v>107</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H50" s="20">
+        <v>10367489</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D51" s="20">
+        <v>107</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H51" s="20">
+        <v>10367490</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D52" s="20">
+        <v>107</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H52" s="20">
+        <v>10367491</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="C53" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D53" s="20">
+        <v>107</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H53" s="20">
+        <v>10367492</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D54" s="20">
+        <v>107</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G54" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" s="20">
+        <v>19044117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D55" s="20">
+        <v>107</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H55" s="20">
+        <v>19044118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="C56" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D56" s="20">
+        <v>107</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H56" s="20">
+        <v>19926542</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="C57" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D57" s="20">
+        <v>107</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H57" s="20">
+        <v>19926545</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="C58" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D58" s="20">
+        <v>107</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="20">
+        <v>19926541</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="C59" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D59" s="20">
+        <v>107</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H59" s="20">
+        <v>19926543</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D60" s="20">
+        <v>107</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H60" s="20">
+        <v>677155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D61" s="20">
+        <v>107</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H61" s="20">
+        <v>677154</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D62" s="20">
+        <v>107</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H62" s="20">
+        <v>19982207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D63" s="20">
+        <v>107</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H63" s="20">
+        <v>19982210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D64" s="20">
+        <v>107</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H64" s="20">
+        <v>18748228</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="C65" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D65" s="20">
+        <v>107</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H65" s="20">
+        <v>18748229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="C66" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D66" s="20">
+        <v>107</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H66" s="20">
+        <v>19623813</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="C67" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D67" s="20">
+        <v>107</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" s="20">
+        <v>19623814</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D68" s="20">
+        <v>107</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G68" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H68" s="20">
+        <v>677164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D69" s="20">
+        <v>107</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H69" s="20">
+        <v>677112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="C70" s="20">
+        <v>2200</v>
+      </c>
+      <c r="D70" s="20">
+        <v>107</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H70" s="20">
+        <v>9271975</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="C71" s="20">
+        <v>3400</v>
+      </c>
+      <c r="D71" s="20">
+        <v>107</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H71" s="20">
+        <v>19869294</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D72" s="20">
+        <v>107</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G72" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H72" s="20">
+        <v>677142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D73" s="20">
+        <v>107</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H73" s="20">
+        <v>677167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C74" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D74" s="20">
+        <v>107</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G74" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H74" s="20">
+        <v>18905784</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D75" s="20">
+        <v>107</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H75" s="20">
+        <v>18905783</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D76" s="20">
+        <v>107</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H76" s="20">
+        <v>18866323</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D77" s="20">
+        <v>107</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="F77" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G77" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H77" s="20">
+        <v>18866324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C78" s="20">
+        <v>3400</v>
+      </c>
+      <c r="D78" s="20">
+        <v>107</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F78" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="H78" s="20">
+        <v>19032282</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="C79" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D79" s="20">
+        <v>107</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H79" s="20">
+        <v>6737411</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C80" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D80" s="20">
+        <v>107</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F80" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G80" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H80" s="20">
+        <v>6737412</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C81" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D81" s="20">
+        <v>107</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H81" s="20">
+        <v>6737413</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C82" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D82" s="20">
+        <v>107</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="G82" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="H82" s="20">
+        <v>6737414</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D83" s="20">
+        <v>107</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H83" s="20">
+        <v>18771406</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B84" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D84" s="20">
+        <v>107</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H84" s="20">
+        <v>18771407</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D85" s="20">
+        <v>107</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H85" s="20">
+        <v>19479016</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D86" s="20">
+        <v>107</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H86" s="20">
+        <v>19479015</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" s="20">
+        <v>1100</v>
+      </c>
+      <c r="D87" s="20">
+        <v>107</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H87" s="20">
+        <v>18905786</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="20">
+        <v>2100</v>
+      </c>
+      <c r="D88" s="20">
+        <v>107</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H88" s="20">
+        <v>18905785</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173102BE-C506-4420-B54D-D84F838C1734}">
   <dimension ref="A1"/>
@@ -2745,7 +6135,2321 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91461CF1-61AE-42DB-80B6-FE37F43F56A8}">
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="21.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D2" s="14">
+        <v>107</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="16">
+        <v>10367489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D3" s="14">
+        <v>107</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="16">
+        <v>10367490</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D4" s="14">
+        <v>107</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="16">
+        <v>10367491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D5" s="14">
+        <v>107</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="16">
+        <v>10367492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3200</v>
+      </c>
+      <c r="D6" s="14">
+        <v>107</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="16">
+        <v>677079</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="16">
+        <v>3100</v>
+      </c>
+      <c r="D7" s="14">
+        <v>107</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="16">
+        <v>677113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D8" s="14">
+        <v>107</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="16">
+        <v>677168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D9" s="14">
+        <v>107</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="16">
+        <v>677140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D10" s="14">
+        <v>107</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="16">
+        <v>677149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D11" s="14">
+        <v>107</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="16">
+        <v>677148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D12" s="14">
+        <v>107</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="16">
+        <v>19044113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D13" s="14">
+        <v>107</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="16">
+        <v>19044114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D14" s="14">
+        <v>107</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="16">
+        <v>19044115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D15" s="14">
+        <v>107</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="16">
+        <v>19044116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D16" s="14">
+        <v>107</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="16">
+        <v>677105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="14">
+        <v>107</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="16">
+        <v>677114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D18" s="14">
+        <v>107</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="16">
+        <v>19289126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D19" s="14">
+        <v>107</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="16">
+        <v>19289125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D20" s="14">
+        <v>107</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="16">
+        <v>18748267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D21" s="14">
+        <v>107</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" s="16">
+        <v>18748268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D22" s="14">
+        <v>107</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22" s="16">
+        <v>18748269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D23" s="14">
+        <v>107</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H23" s="16">
+        <v>18748270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D24" s="14">
+        <v>107</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="16">
+        <v>18748271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D25" s="14">
+        <v>107</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" s="16">
+        <v>18748272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D26" s="14">
+        <v>107</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="16">
+        <v>677138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D27" s="14">
+        <v>107</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H27" s="16">
+        <v>677141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D28" s="14">
+        <v>107</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H28" s="16">
+        <v>677150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B29" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D29" s="14">
+        <v>107</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="H29" s="16">
+        <v>19926542</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" t="s">
+        <v>245</v>
+      </c>
+      <c r="C30" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D30" s="14">
+        <v>107</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="H30" s="16">
+        <v>19926545</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D31" s="14">
+        <v>107</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" s="16">
+        <v>19926541</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" t="s">
+        <v>247</v>
+      </c>
+      <c r="C32" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D32" s="14">
+        <v>107</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" s="16">
+        <v>19926543</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" t="s">
+        <v>259</v>
+      </c>
+      <c r="C33" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D33" s="14">
+        <v>107</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H33" s="16">
+        <v>9697138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B34" t="s">
+        <v>260</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D34" s="14">
+        <v>107</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" s="16">
+        <v>9697137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B35" t="s">
+        <v>261</v>
+      </c>
+      <c r="C35" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D35" s="14">
+        <v>107</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="16">
+        <v>18772023</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D36" s="14">
+        <v>107</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="16">
+        <v>18772024</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D37" s="14">
+        <v>107</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H37" s="16">
+        <v>18748228</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B38" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D38" s="14">
+        <v>107</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" s="16">
+        <v>18748229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" t="s">
+        <v>263</v>
+      </c>
+      <c r="C39" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D39" s="14">
+        <v>107</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H39" s="16">
+        <v>19623813</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>264</v>
+      </c>
+      <c r="C40" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D40" s="14">
+        <v>107</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" s="16">
+        <v>19623814</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D41" s="14">
+        <v>107</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H41" s="16">
+        <v>677164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D42" s="14">
+        <v>107</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H42" s="16">
+        <v>677112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" s="16">
+        <v>2200</v>
+      </c>
+      <c r="D43" s="14">
+        <v>107</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H43" s="16">
+        <v>9271975</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B44" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="16">
+        <v>3400</v>
+      </c>
+      <c r="D44" s="14">
+        <v>107</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="16">
+        <v>19869294</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D45" s="14">
+        <v>107</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H45" s="16">
+        <v>19865894</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D46" s="14">
+        <v>107</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H46" s="16">
+        <v>19865893</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D47" s="14">
+        <v>107</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H47" s="16">
+        <v>677153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B48" t="s">
+        <v>231</v>
+      </c>
+      <c r="C48" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D48" s="14">
+        <v>107</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H48" s="16">
+        <v>677124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D49" s="14">
+        <v>107</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H49" s="16">
+        <v>677155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D50" s="14">
+        <v>107</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H50" s="16">
+        <v>677154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D51" s="14">
+        <v>107</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H51" s="16">
+        <v>18771404</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D52" s="14">
+        <v>107</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H52" s="16">
+        <v>18771405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D53" s="14">
+        <v>107</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H53" s="16">
+        <v>18771406</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D54" s="14">
+        <v>107</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H54" s="16">
+        <v>18771407</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D55" s="14">
+        <v>107</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55" s="16">
+        <v>18905782</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B56" t="s">
+        <v>231</v>
+      </c>
+      <c r="C56" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D56" s="14">
+        <v>107</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="16">
+        <v>18905781</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D57" s="14">
+        <v>107</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H57" s="16">
+        <v>18905784</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B58" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D58" s="14">
+        <v>107</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H58" s="16">
+        <v>18905783</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D59" s="14">
+        <v>107</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H59" s="16">
+        <v>18905786</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B60" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D60" s="14">
+        <v>107</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H60" s="16">
+        <v>18905785</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D61" s="14">
+        <v>107</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H61" s="16">
+        <v>18905788</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" t="s">
+        <v>231</v>
+      </c>
+      <c r="C62" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D62" s="14">
+        <v>107</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H62" s="16">
+        <v>18905787</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C63" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D63" s="14">
+        <v>107</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H63" s="16">
+        <v>6737419</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" t="s">
+        <v>231</v>
+      </c>
+      <c r="C64" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D64" s="14">
+        <v>107</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H64" s="16">
+        <v>6737420</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D65" s="14">
+        <v>107</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G65" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H65" s="16">
+        <v>677142</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D66" s="14">
+        <v>107</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H66" s="16">
+        <v>677167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D67" s="14">
+        <v>107</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="H67" s="16">
+        <v>18839472</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" t="s">
+        <v>231</v>
+      </c>
+      <c r="C68" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D68" s="14">
+        <v>107</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="H68" s="16">
+        <v>18839473</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D69" s="14">
+        <v>107</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H69" s="16">
+        <v>18866323</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B70" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D70" s="14">
+        <v>107</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H70" s="16">
+        <v>18866324</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B71" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D71" s="14">
+        <v>107</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H71" s="16">
+        <v>19044117</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B72" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D72" s="14">
+        <v>107</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H72" s="16">
+        <v>19044118</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" t="s">
+        <v>36</v>
+      </c>
+      <c r="C73" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D73" s="14">
+        <v>107</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H73" s="16">
+        <v>19479016</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B74" t="s">
+        <v>231</v>
+      </c>
+      <c r="C74" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D74" s="14">
+        <v>107</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H74" s="16">
+        <v>19479015</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" t="s">
+        <v>36</v>
+      </c>
+      <c r="C75" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D75" s="14">
+        <v>107</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H75" s="16">
+        <v>19982207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D76" s="14">
+        <v>107</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="16">
+        <v>19982210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" t="s">
+        <v>36</v>
+      </c>
+      <c r="C77" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D77" s="14">
+        <v>107</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="16">
+        <v>6737415</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C78" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D78" s="14">
+        <v>107</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H78" s="16">
+        <v>6737416</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" t="s">
+        <v>36</v>
+      </c>
+      <c r="C79" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D79" s="14">
+        <v>107</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H79" s="16">
+        <v>6737417</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" t="s">
+        <v>231</v>
+      </c>
+      <c r="C80" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D80" s="14">
+        <v>107</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H80" s="16">
+        <v>6737418</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B81" t="s">
+        <v>272</v>
+      </c>
+      <c r="C81" s="16">
+        <v>3400</v>
+      </c>
+      <c r="D81" s="14">
+        <v>107</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H81" s="16">
+        <v>18772025</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" t="s">
+        <v>274</v>
+      </c>
+      <c r="C82" s="16">
+        <v>3400</v>
+      </c>
+      <c r="D82" s="14">
+        <v>107</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H82" s="16">
+        <v>19032282</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B83" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D83" s="14">
+        <v>107</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H83" s="16">
+        <v>19470810</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B84" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D84" s="14">
+        <v>107</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H84" s="16">
+        <v>19470811</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" t="s">
+        <v>275</v>
+      </c>
+      <c r="C85" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D85" s="14">
+        <v>107</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H85" s="16">
+        <v>6737411</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B86" t="s">
+        <v>276</v>
+      </c>
+      <c r="C86" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D86" s="14">
+        <v>107</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H86" s="16">
+        <v>6737412</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B87" t="s">
+        <v>277</v>
+      </c>
+      <c r="C87" s="16">
+        <v>1100</v>
+      </c>
+      <c r="D87" s="14">
+        <v>107</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" s="16">
+        <v>6737413</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B88" t="s">
+        <v>278</v>
+      </c>
+      <c r="C88" s="16">
+        <v>2100</v>
+      </c>
+      <c r="D88" s="14">
+        <v>107</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H88" s="16">
+        <v>6737414</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="cb6380d2-b01f-4e04-9200-9666676ed141" xsi:nil="true"/>
@@ -2753,7 +8457,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A49252DC7531642B064D59214E738D4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e90bbfbf4f52bf4a6656f5589d033bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cb6380d2-b01f-4e04-9200-9666676ed141" xmlns:ns4="f068c7d5-04e7-4821-88a1-b1f97a388bb7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d814bd8026fe29e70e1bc18c824ed2a7" ns3:_="" ns4:_="">
     <xsd:import namespace="cb6380d2-b01f-4e04-9200-9666676ed141"/>
@@ -3006,16 +8710,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A62760-3B76-45B2-B7CB-74304B7ECF2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="f068c7d5-04e7-4821-88a1-b1f97a388bb7"/>
@@ -3032,7 +8735,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6848DD44-78B0-4924-8517-B02B8138DA94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3049,12 +8752,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>